--- a/pacjenci/MATYLDA MOROWIEC.xlsx
+++ b/pacjenci/MATYLDA MOROWIEC.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">

--- a/pacjenci/MATYLDA MOROWIEC.xlsx
+++ b/pacjenci/MATYLDA MOROWIEC.xlsx
@@ -413,279 +413,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>07.07.2020</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina- ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  60 min od podania 18F-FDG. Glikemia: 112mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywne metabolicznie węzły chłonne przedziału III-V i nadobojczykowe po stronie lewej wielkości do 23x20x31mm wg PET, SUV max do 9,6. Aktywne metabolicznie węzły chłonne przedziału IV po stronie prawej wielkości do 16x15mm wg PET, SUV max do 8,3. Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym (SUV max 5,2) i lewym (SUV max 5,3) - do kontroli.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawostronne skrzywienie przegrody nosa.   Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - przytchawicze górne lewe wielkości do 14mm wg PET, SUV max 5,5 - przytchawicze prawe wielkości do 14mm wg PET, SUV max do 4,8 - w śródpiersiu przednim po stronie lewej wielkości do 31x26mm wg PET, SUV max do 12,1 - w śródpiersiu przednim po stronie prawej wielkości do 21mm wg PET, SUV max do 5,6 - przy łuku aorty wielkości 10mm wg PET, SUV max 4,9 - przymostkowy po stronie lewej wielkości 16mm, SUV max 8,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym.  Wartości referencyjne: MBPS SUVmax do 2,0 Prawy płat wątroby SUVmax do 2,5.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego powyżej poziomu przepony.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>12.1</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>14.09.2020</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina- ocena wczesnej odpowiedzi na stosowane leczenie.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 88mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Miernie pobudzone metabolicznie węzły chłonne V i nadobojczykowe po stronie lewej średnicy do 13mm, SUV max do 2,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę prawą.   Klatka piersiowa i śródpiersie: Aktywna metaboliczne niejednorodna zmiana guzkowa - obwodowo w segmencie 9 płuca prawego średnicy 20mm, SUV max 3,3 - zmiany naciekowo-zapalne? w przebiegu choroby podstawowej? - do weryfikacji/oceny klinicznej i kontroli po leczeniu p/zapalnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim wielkości 39x24mm. Drobne węzły chłonne w śródpiersiu przednim i przy łuku aorty średnicy do 13mm. Drobne zmiany włókniste nadprzeponowo po stronie lewej.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Rozlanie zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym.  Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Nieliczne drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 2,5.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnej metaboliczne zmiany w płucu prawym - zmiana naciekowo-zapalna? w przebiegu choroby podstawowej? - do weryfikacji/oceny klinicznej i kontroli po leczeniu p/zapalnym.  Poza tym uwidoczniono dobrą odpowiedź metaboliczną zmian węzłowych na stosowane leczenie. Masa miękkotkankowa w śródpiersiu i węzły chłonne szyjne do kontroli.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3.3</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>30.11.2020</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina - ocena odpowiedzi na stosowane leczenie po 4 cyklach chemioterapii.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  58min od podania 18F-FDG. Glikemia:100mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę prawą.  Drobne węzły szyjne średnicy do 10mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim wielkości 35x24mm. Węzły chłonne w śródpiersiu wielkości do 12mm i przy łuku aorty średnicy do 15mm. Niewielkie zmiany włókniste nadprzeponowo po stronie lewej.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Rozlanie zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym.  Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Nieliczne drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.  Inne: Zwiększona aktywność metaboliczna w tkance brunatnej szyi, karku i klatki piersiowej, SUV max do 9,2.  Wartości referencyjne: MBPS SUVmax do 1,6; Prawy płat wątroby SUVmax do 2,1.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną na stosowane leczenie. Masa miękkotkankowa w śródpiersiu do kontroli.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>04.01.2021</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina - ocena remisji choroby po zakończeniu Chth.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 98mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę prawą.  Drobne węzły szyjne średnicy do 10mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim wielkości 31x18mm. Węzły chłonne w śródpiersiu wielkości do 12mm oraz przy łuku aorty śr. do 8mm. Niewielkie zmiany włókniste nadprzeponowo po stronie lewej.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Rozlanie zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym.  Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Nieliczne drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.  Inne: Zwiększona aktywność metaboliczna w tkance brunatnej szyi, karku i klatki piersiowej, SUV max do 5,2.  Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 2,4.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono cech aktywnej metabolicznie choroby chłoniakowej. Masa miękkotkankowa w śródpiersiu do kontroli.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5.2</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>17.06.2021</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina - ocena remisji choroby 3  miesiące po IFRT.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  62min od podania 18F-FDG. Glikemia: 86mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Symetryczna aktywność metaboliczna w strukturach pierścienia Waldeyera, SUV max 4,8. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę prawą.  Drobne węzły szyjne średnicy do 10mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim wielkości 28x20mm. Węzły chłonne w śródpiersiu wielkości do 8mm. Niewielkie zmiany włókniste nadprzeponowo po stronie lewej.  Brzuch i miednica: Odcinkowa aktywność metaboliczna w topografii pętli jelit, SUV max do 3,7  - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Nieliczne drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 1,4; Prawy płat wątroby SUVmax do 2,5.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono cech aktywnej metabolicznie choroby chłoniakowej. Masa miękkotkankowa w śródpiersiu do kontroli.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>4.8</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/MATYLDA MOROWIEC.xlsx
+++ b/pacjenci/MATYLDA MOROWIEC.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  60 min od podania 18F-FDG. Glikemia: 112mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne przedziału III-V i nadobojczykowe po stronie lewej wielkości do 23x20x31mm wg PET, SUV max do 9,6. Aktywne metabolicznie węzły chłonne przedziału IV po stronie prawej wielkości do 16x15mm wg PET, SUV max do 8,3. Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym (SUV max 5,2) i lewym (SUV max 5,3) - do kontroli.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawostronne skrzywienie przegrody nosa.   Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - przytchawicze górne lewe wielkości do 14mm wg PET, SUV max 5,5 - przytchawicze prawe wielkości do 14mm wg PET, SUV max do 4,8 - w śródpiersiu przednim po stronie lewej wielkości do 31x26mm wg PET, SUV max do 12,1 - w śródpiersiu przednim po stronie prawej wielkości do 21mm wg PET, SUV max do 5,6 - przy łuku aorty wielkości 10mm wg PET, SUV max 4,9 - przymostkowy po stronie lewej wielkości 16mm, SUV max 8,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym.  Wartości referencyjne: MBPS SUVmax do 2,0 Prawy płat wątroby SUVmax do 2,5.</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne przedziału III-V i nadobojczykowe po stronie lewej wielkości do 23x20x31mm wg PET, SUV max do 9,6. Aktywne metabolicznie węzły chłonne przedziału IV po stronie prawej wielkości do 16x15mm wg PET, SUV max do 8,3. Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym (SUV max 5,2) i lewym (SUV max 5,3) - do kontroli.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawostronne skrzywienie przegrody nosa.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - przytchawicze górne lewe wielkości do 14mm wg PET, SUV max 5,5 - przytchawicze prawe wielkości do 14mm wg PET, SUV max do 4,8 - w śródpiersiu przednim po stronie lewej wielkości do 31x26mm wg PET, SUV max do 12,1 - w śródpiersiu przednim po stronie prawej wielkości do 21mm wg PET, SUV max do 5,6 - przy łuku aorty wielkości 10mm wg PET, SUV max 4,9 - przymostkowy po stronie lewej wielkości 16mm, SUV max 8,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego powyżej poziomu przepony.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>12.1</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 88mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Miernie pobudzone metabolicznie węzły chłonne V i nadobojczykowe po stronie lewej średnicy do 13mm, SUV max do 2,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę prawą.   Klatka piersiowa i śródpiersie: Aktywna metaboliczne niejednorodna zmiana guzkowa - obwodowo w segmencie 9 płuca prawego średnicy 20mm, SUV max 3,3 - zmiany naciekowo-zapalne? w przebiegu choroby podstawowej? - do weryfikacji/oceny klinicznej i kontroli po leczeniu p/zapalnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim wielkości 39x24mm. Drobne węzły chłonne w śródpiersiu przednim i przy łuku aorty średnicy do 13mm. Drobne zmiany włókniste nadprzeponowo po stronie lewej.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Rozlanie zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym.  Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Nieliczne drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 2,5.</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie węzły chłonne V i nadobojczykowe po stronie lewej średnicy do 13mm, SUV max do 2,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę prawą.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Aktywna metaboliczne niejednorodna zmiana guzkowa - obwodowo w segmencie 9 płuca prawego średnicy 20mm, SUV max 3,3 - zmiany naciekowo-zapalne? w przebiegu choroby podstawowej? - do weryfikacji/oceny klinicznej i kontroli po leczeniu p/zapalnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim wielkości 39x24mm. Drobne węzły chłonne w śródpiersiu przednim i przy łuku aorty średnicy do 13mm. Drobne zmiany włókniste nadprzeponowo po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym.  Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Nieliczne drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnej metaboliczne zmiany w płucu prawym - zmiana naciekowo-zapalna? w przebiegu choroby podstawowej? - do weryfikacji/oceny klinicznej i kontroli po leczeniu p/zapalnym.  Poza tym uwidoczniono dobrą odpowiedź metaboliczną zmian węzłowych na stosowane leczenie. Masa miękkotkankowa w śródpiersiu i węzły chłonne szyjne do kontroli.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>3.3</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  58min od podania 18F-FDG. Glikemia:100mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę prawą.  Drobne węzły szyjne średnicy do 10mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim wielkości 35x24mm. Węzły chłonne w śródpiersiu wielkości do 12mm i przy łuku aorty średnicy do 15mm. Niewielkie zmiany włókniste nadprzeponowo po stronie lewej.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Rozlanie zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym.  Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Nieliczne drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.  Inne: Zwiększona aktywność metaboliczna w tkance brunatnej szyi, karku i klatki piersiowej, SUV max do 9,2.  Wartości referencyjne: MBPS SUVmax do 1,6; Prawy płat wątroby SUVmax do 2,1.</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę prawą.  Drobne węzły szyjne średnicy do 10mm.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim wielkości 35x24mm. Węzły chłonne w śródpiersiu wielkości do 12mm i przy łuku aorty średnicy do 15mm. Niewielkie zmiany włókniste nadprzeponowo po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym.  Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Nieliczne drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.  Inne: Zwiększona aktywność metaboliczna w tkance brunatnej szyi, karku i klatki piersiowej, SUV max do 9,2.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną na stosowane leczenie. Masa miękkotkankowa w śródpiersiu do kontroli.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>9.199999999999999</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 98mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę prawą.  Drobne węzły szyjne średnicy do 10mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim wielkości 31x18mm. Węzły chłonne w śródpiersiu wielkości do 12mm oraz przy łuku aorty śr. do 8mm. Niewielkie zmiany włókniste nadprzeponowo po stronie lewej.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Rozlanie zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym.  Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Nieliczne drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.  Inne: Zwiększona aktywność metaboliczna w tkance brunatnej szyi, karku i klatki piersiowej, SUV max do 5,2.  Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 2,4.</t>
+          <t>98</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę prawą.  Drobne węzły szyjne średnicy do 10mm.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim wielkości 31x18mm. Węzły chłonne w śródpiersiu wielkości do 12mm oraz przy łuku aorty śr. do 8mm. Niewielkie zmiany włókniste nadprzeponowo po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym.  Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Nieliczne drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.  Inne: Zwiększona aktywność metaboliczna w tkance brunatnej szyi, karku i klatki piersiowej, SUV max do 5,2.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono cech aktywnej metabolicznie choroby chłoniakowej. Masa miękkotkankowa w śródpiersiu do kontroli.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>5.2</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  62min od podania 18F-FDG. Glikemia: 86mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Symetryczna aktywność metaboliczna w strukturach pierścienia Waldeyera, SUV max 4,8. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę prawą.  Drobne węzły szyjne średnicy do 10mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim wielkości 28x20mm. Węzły chłonne w śródpiersiu wielkości do 8mm. Niewielkie zmiany włókniste nadprzeponowo po stronie lewej.  Brzuch i miednica: Odcinkowa aktywność metaboliczna w topografii pętli jelit, SUV max do 3,7  - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Nieliczne drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 1,4; Prawy płat wątroby SUVmax do 2,5.</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Symetryczna aktywność metaboliczna w strukturach pierścienia Waldeyera, SUV max 4,8. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę prawą.  Drobne węzły szyjne średnicy do 10mm.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim wielkości 28x20mm. Węzły chłonne w śródpiersiu wielkości do 8mm. Niewielkie zmiany włókniste nadprzeponowo po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Odcinkowa aktywność metaboliczna w topografii pętli jelit, SUV max do 3,7  - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Nieliczne drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono cech aktywnej metabolicznie choroby chłoniakowej. Masa miękkotkankowa w śródpiersiu do kontroli.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>4.8</v>
       </c>
     </row>
